--- a/doc/K2CoverageResults.xlsx
+++ b/doc/K2CoverageResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\openSUSE-Tumbleweed\home\ssilvestri\research\Kappa2\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981AED69-614A-4649-92A9-CF41E1E6FE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E953A69-29D3-4E1F-AB57-CA22EACE1747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{834EB836-E108-4946-BBD2-E48878051BC8}"/>
   </bookViews>
@@ -283,9 +283,16 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>K2Stream!$A$2:$A$12</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>K2Stream!$A$2:$A$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>K2Stream!$A$2:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>connections.rs</c:v>
                 </c:pt>
@@ -312,19 +319,23 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>stream_controller.rs</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Totale</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>K2Stream!$C$2:$C$12</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>K2Stream!$C$2:$C$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>K2Stream!$C$2:$C$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>25</c:v>
                 </c:pt>
@@ -351,9 +362,6 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -382,9 +390,16 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>K2Stream!$A$2:$A$12</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>K2Stream!$A$2:$A$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>K2Stream!$A$2:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>connections.rs</c:v>
                 </c:pt>
@@ -411,19 +426,23 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>stream_controller.rs</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Totale</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>K2Stream!$F$2:$F$12</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>K2Stream!$F$2:$F$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>K2Stream!$F$2:$F$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>134</c:v>
                 </c:pt>
@@ -434,7 +453,7 @@
                   <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>45</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>167</c:v>
@@ -450,9 +469,6 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>253</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -481,9 +497,16 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>K2Stream!$A$2:$A$12</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>K2Stream!$A$2:$A$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>K2Stream!$A$2:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>connections.rs</c:v>
                 </c:pt>
@@ -510,19 +533,23 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>stream_controller.rs</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Totale</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>K2Stream!$I$2:$I$12</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>K2Stream!$I$2:$I$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>K2Stream!$I$2:$I$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>308</c:v>
                 </c:pt>
@@ -533,7 +560,7 @@
                   <c:v>121</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>67</c:v>
+                  <c:v>181</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>268</c:v>
@@ -549,9 +576,6 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>651</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2311</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -883,7 +907,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.44776119402985</c:v>
+                  <c:v>95.58011049723757</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -1184,10 +1208,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>33.232366940718308</c:v>
+                  <c:v>38.515463917525771</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>66.767633059281692</c:v>
+                  <c:v>61.484536082474229</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5454,34 +5478,34 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="F5">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="1"/>
-        <v>17.777777777777779</v>
+        <v>91.428571428571431</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>173</v>
       </c>
       <c r="I5">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="J5" s="1">
         <f t="shared" si="2"/>
-        <v>10.44776119402985</v>
+        <v>95.58011049723757</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -5665,7 +5689,7 @@
       </c>
       <c r="B12">
         <f>SUM(B2:B10)</f>
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C12">
         <f t="shared" ref="C12:I12" si="3">SUM(C2:C10)</f>
@@ -5673,31 +5697,31 @@
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>27.485380116959064</v>
+        <v>30.994152046783626</v>
       </c>
       <c r="E12">
         <f t="shared" si="3"/>
-        <v>378</v>
+        <v>434</v>
       </c>
       <c r="F12">
         <f t="shared" si="3"/>
-        <v>1112</v>
+        <v>1137</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="1"/>
-        <v>33.992805755395686</v>
+        <v>38.170624450307827</v>
       </c>
       <c r="H12">
         <f t="shared" si="3"/>
-        <v>768</v>
+        <v>934</v>
       </c>
       <c r="I12">
         <f t="shared" si="3"/>
-        <v>2311</v>
+        <v>2425</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" si="2"/>
-        <v>33.232366940718308</v>
+        <v>38.515463917525771</v>
       </c>
       <c r="K12" t="s">
         <v>23</v>
@@ -5706,7 +5730,7 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J13" s="1">
         <f>100-J12</f>
-        <v>66.767633059281692</v>
+        <v>61.484536082474229</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -5718,7 +5742,7 @@
       </c>
       <c r="M18">
         <f>I12-I4</f>
-        <v>2190</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="19" spans="12:13" x14ac:dyDescent="0.3">

--- a/doc/K2CoverageResults.xlsx
+++ b/doc/K2CoverageResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\openSUSE-Tumbleweed\home\ssilvestri\research\Kappa2\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E953A69-29D3-4E1F-AB57-CA22EACE1747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5312F2A0-5D23-4BCA-B510-48CEABD5449D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{834EB836-E108-4946-BBD2-E48878051BC8}"/>
   </bookViews>
@@ -337,25 +337,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>25</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>17</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>28</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>9</c:v>
@@ -444,25 +444,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>134</c:v>
+                  <c:v>137</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>63</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>70</c:v>
+                  <c:v>91</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>167</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>214</c:v>
+                  <c:v>205</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>164</c:v>
+                  <c:v>244</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>51</c:v>
@@ -551,31 +551,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>308</c:v>
+                  <c:v>311</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>121</c:v>
+                  <c:v>126</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>181</c:v>
+                  <c:v>247</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>268</c:v>
+                  <c:v>267</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>410</c:v>
+                  <c:v>393</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>360</c:v>
+                  <c:v>536</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>651</c:v>
+                  <c:v>650</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -898,25 +898,25 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>95.779220779220779</c:v>
+                  <c:v>94.855305466237937</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>32.608695652173914</c:v>
+                  <c:v>53.333333333333336</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>95.58011049723757</c:v>
+                  <c:v>98.785425101214571</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>91.463414634146346</c:v>
+                  <c:v>94.402035623409674</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>88.619402985074629</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>95</c:v>
@@ -1208,10 +1208,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>38.515463917525771</c:v>
+                  <c:v>55.932203389830505</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>61.484536082474229</c:v>
+                  <c:v>44.067796610169495</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5376,31 +5376,31 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1">
         <f>B2/C2*100</f>
-        <v>88</v>
+        <v>84.615384615384613</v>
       </c>
       <c r="E2">
         <v>129</v>
       </c>
       <c r="F2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G2" s="1">
         <f>E2/F2*100</f>
-        <v>96.268656716417908</v>
+        <v>94.160583941605836</v>
       </c>
       <c r="H2">
         <v>295</v>
       </c>
       <c r="I2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J2" s="1">
         <f>H2/I2*100</f>
-        <v>95.779220779220779</v>
+        <v>94.855305466237937</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -5418,24 +5418,24 @@
         <v>33.333333333333329</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" ref="G3:G12" si="1">E3/F3*100</f>
-        <v>33.333333333333329</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J3" s="1">
         <f t="shared" ref="J3:J12" si="2">H3/I3*100</f>
-        <v>32.608695652173914</v>
+        <v>53.333333333333336</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -5446,7 +5446,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
@@ -5456,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="1"/>
@@ -5466,7 +5466,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J4" s="1">
         <f t="shared" si="2"/>
@@ -5478,34 +5478,34 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>90.909090909090907</v>
       </c>
       <c r="E5">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="F5">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="1"/>
-        <v>91.428571428571431</v>
+        <v>96.703296703296701</v>
       </c>
       <c r="H5">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I5">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="J5" s="1">
         <f t="shared" si="2"/>
-        <v>95.58011049723757</v>
+        <v>98.785425101214571</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -5536,7 +5536,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" si="2"/>
@@ -5551,31 +5551,31 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" si="0"/>
-        <v>82.35294117647058</v>
+        <v>87.5</v>
       </c>
       <c r="E7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F7">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="1"/>
-        <v>86.915887850467286</v>
+        <v>89.756097560975618</v>
       </c>
       <c r="H7">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="I7">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="J7" s="1">
         <f t="shared" si="2"/>
-        <v>91.463414634146346</v>
+        <v>94.402035623409674</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -5583,34 +5583,34 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>86.486486486486484</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="F8">
-        <v>164</v>
+        <v>244</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>91.393442622950815</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="I8">
-        <v>360</v>
+        <v>536</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>88.619402985074629</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -5676,7 +5676,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="J10" s="1">
         <f t="shared" si="2"/>
@@ -5689,39 +5689,39 @@
       </c>
       <c r="B12">
         <f>SUM(B2:B10)</f>
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C12">
         <f t="shared" ref="C12:I12" si="3">SUM(C2:C10)</f>
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>30.994152046783626</v>
+        <v>47.802197802197803</v>
       </c>
       <c r="E12">
         <f t="shared" si="3"/>
-        <v>434</v>
+        <v>682</v>
       </c>
       <c r="F12">
         <f t="shared" si="3"/>
-        <v>1137</v>
+        <v>1234</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="1"/>
-        <v>38.170624450307827</v>
+        <v>55.267423014586711</v>
       </c>
       <c r="H12">
         <f t="shared" si="3"/>
-        <v>934</v>
+        <v>1485</v>
       </c>
       <c r="I12">
         <f t="shared" si="3"/>
-        <v>2425</v>
+        <v>2655</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" si="2"/>
-        <v>38.515463917525771</v>
+        <v>55.932203389830505</v>
       </c>
       <c r="K12" t="s">
         <v>23</v>
@@ -5730,7 +5730,7 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J13" s="1">
         <f>100-J12</f>
-        <v>61.484536082474229</v>
+        <v>44.067796610169495</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="M18">
         <f>I12-I4</f>
-        <v>2304</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="19" spans="12:13" x14ac:dyDescent="0.3">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="M19">
         <f>I4</f>
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/doc/K2CoverageResults.xlsx
+++ b/doc/K2CoverageResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\openSUSE-Tumbleweed\home\ssilvestri\research\Kappa2\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5312F2A0-5D23-4BCA-B510-48CEABD5449D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382EE6BE-A48C-47B3-B181-9E78C9810C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{834EB836-E108-4946-BBD2-E48878051BC8}"/>
   </bookViews>
@@ -349,13 +349,13 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>37</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>9</c:v>
@@ -456,13 +456,13 @@
                   <c:v>91</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>167</c:v>
+                  <c:v>208</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>205</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>244</c:v>
+                  <c:v>239</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>51</c:v>
@@ -563,13 +563,13 @@
                   <c:v>247</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>267</c:v>
+                  <c:v>395</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>393</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>536</c:v>
+                  <c:v>530</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>80</c:v>
@@ -910,13 +910,13 @@
                   <c:v>98.785425101214571</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>44.303797468354425</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>94.402035623409674</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>88.619402985074629</c:v>
+                  <c:v>89.056603773584911</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>95</c:v>
@@ -1208,10 +1208,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>55.932203389830505</c:v>
+                  <c:v>59.668707238026656</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44.067796610169495</c:v>
+                  <c:v>40.331292761973344</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5513,34 +5513,34 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>34.375</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F6">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>40.865384615384613</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="I6">
-        <v>267</v>
+        <v>395</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>44.303797468354425</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -5586,31 +5586,31 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>86.486486486486484</v>
+        <v>88.888888888888886</v>
       </c>
       <c r="E8">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F8">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="1"/>
-        <v>91.393442622950815</v>
+        <v>92.468619246861934</v>
       </c>
       <c r="H8">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="I8">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" si="2"/>
-        <v>88.619402985074629</v>
+        <v>89.056603773584911</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -5689,39 +5689,39 @@
       </c>
       <c r="B12">
         <f>SUM(B2:B10)</f>
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C12">
         <f t="shared" ref="C12:I12" si="3">SUM(C2:C10)</f>
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>47.802197802197803</v>
+        <v>52.972972972972975</v>
       </c>
       <c r="E12">
         <f t="shared" si="3"/>
-        <v>682</v>
+        <v>765</v>
       </c>
       <c r="F12">
         <f t="shared" si="3"/>
-        <v>1234</v>
+        <v>1270</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="1"/>
-        <v>55.267423014586711</v>
+        <v>60.236220472440948</v>
       </c>
       <c r="H12">
         <f t="shared" si="3"/>
-        <v>1485</v>
+        <v>1657</v>
       </c>
       <c r="I12">
         <f t="shared" si="3"/>
-        <v>2655</v>
+        <v>2777</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" si="2"/>
-        <v>55.932203389830505</v>
+        <v>59.668707238026656</v>
       </c>
       <c r="K12" t="s">
         <v>23</v>
@@ -5730,7 +5730,7 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J13" s="1">
         <f>100-J12</f>
-        <v>44.067796610169495</v>
+        <v>40.331292761973344</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="M18">
         <f>I12-I4</f>
-        <v>2529</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="19" spans="12:13" x14ac:dyDescent="0.3">

--- a/doc/K2CoverageResults.xlsx
+++ b/doc/K2CoverageResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\openSUSE-Tumbleweed\home\ssilvestri\research\Kappa2\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382EE6BE-A48C-47B3-B181-9E78C9810C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9573B20C-E17D-434E-97E2-7D4817D99394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{834EB836-E108-4946-BBD2-E48878051BC8}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{834EB836-E108-4946-BBD2-E48878051BC8}"/>
   </bookViews>
   <sheets>
     <sheet name="K2Stream" sheetId="1" r:id="rId1"/>
@@ -349,7 +349,7 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>32</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>16</c:v>
@@ -456,7 +456,7 @@
                   <c:v>91</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>208</c:v>
+                  <c:v>225</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>205</c:v>
@@ -563,7 +563,7 @@
                   <c:v>247</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>395</c:v>
+                  <c:v>467</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>393</c:v>
@@ -910,7 +910,7 @@
                   <c:v>98.785425101214571</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>44.303797468354425</c:v>
+                  <c:v>62.098501070663815</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>94.402035623409674</c:v>
@@ -1208,10 +1208,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>59.668707238026656</c:v>
+                  <c:v>62.197262197262191</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>40.331292761973344</c:v>
+                  <c:v>37.802737802737809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5513,34 +5513,34 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>34.375</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="E6">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="F6">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="1"/>
-        <v>40.865384615384613</v>
+        <v>59.111111111111114</v>
       </c>
       <c r="H6">
-        <v>175</v>
+        <v>290</v>
       </c>
       <c r="I6">
-        <v>395</v>
+        <v>467</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" si="2"/>
-        <v>44.303797468354425</v>
+        <v>62.098501070663815</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -5689,39 +5689,39 @@
       </c>
       <c r="B12">
         <f>SUM(B2:B10)</f>
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C12">
         <f t="shared" ref="C12:I12" si="3">SUM(C2:C10)</f>
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>52.972972972972975</v>
+        <v>56.451612903225815</v>
       </c>
       <c r="E12">
         <f t="shared" si="3"/>
-        <v>765</v>
+        <v>813</v>
       </c>
       <c r="F12">
         <f t="shared" si="3"/>
-        <v>1270</v>
+        <v>1287</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="1"/>
-        <v>60.236220472440948</v>
+        <v>63.170163170163171</v>
       </c>
       <c r="H12">
         <f t="shared" si="3"/>
-        <v>1657</v>
+        <v>1772</v>
       </c>
       <c r="I12">
         <f t="shared" si="3"/>
-        <v>2777</v>
+        <v>2849</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" si="2"/>
-        <v>59.668707238026656</v>
+        <v>62.197262197262191</v>
       </c>
       <c r="K12" t="s">
         <v>23</v>
@@ -5730,7 +5730,7 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J13" s="1">
         <f>100-J12</f>
-        <v>40.331292761973344</v>
+        <v>37.802737802737809</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="M18">
         <f>I12-I4</f>
-        <v>2651</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="19" spans="12:13" x14ac:dyDescent="0.3">

--- a/doc/K2CoverageResults.xlsx
+++ b/doc/K2CoverageResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\openSUSE-Tumbleweed\home\ssilvestri\research\Kappa2\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9573B20C-E17D-434E-97E2-7D4817D99394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D1BD6A-78B6-47B1-B898-5F419B1BAA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{834EB836-E108-4946-BBD2-E48878051BC8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{834EB836-E108-4946-BBD2-E48878051BC8}"/>
   </bookViews>
   <sheets>
     <sheet name="K2Stream" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="KCoder" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -156,13 +157,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -349,7 +349,7 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>33</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>16</c:v>
@@ -361,7 +361,7 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>44</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -456,7 +456,7 @@
                   <c:v>91</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>225</c:v>
+                  <c:v>230</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>205</c:v>
@@ -468,7 +468,7 @@
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>253</c:v>
+                  <c:v>444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -563,7 +563,7 @@
                   <c:v>247</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>467</c:v>
+                  <c:v>466</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>393</c:v>
@@ -575,7 +575,7 @@
                   <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>650</c:v>
+                  <c:v>1189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -901,7 +901,7 @@
                   <c:v>94.855305466237937</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53.333333333333336</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -910,19 +910,19 @@
                   <c:v>98.785425101214571</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>62.098501070663815</c:v>
+                  <c:v>81.330472103004297</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>94.402035623409674</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>89.056603773584911</c:v>
+                  <c:v>89.433962264150949</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>78.132884777123635</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1171,6 +1171,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-E527-46D0-921C-72A5D0E1E2A4}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1186,6 +1191,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-E527-46D0-921C-72A5D0E1E2A4}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -1208,10 +1218,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>62.197262197262191</c:v>
+                  <c:v>82.521405373486871</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>37.802737802737809</c:v>
+                  <c:v>17.478594626513129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5418,24 +5428,24 @@
         <v>33.333333333333329</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" ref="G3:G12" si="1">E3/F3*100</f>
-        <v>50</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="H3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I3">
         <v>45</v>
       </c>
       <c r="J3" s="1">
         <f t="shared" ref="J3:J12" si="2">H3/I3*100</f>
-        <v>53.333333333333336</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -5513,34 +5523,34 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>54.54545454545454</v>
+        <v>65.714285714285708</v>
       </c>
       <c r="E6">
-        <v>133</v>
+        <v>186</v>
       </c>
       <c r="F6">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="1"/>
-        <v>59.111111111111114</v>
+        <v>80.869565217391298</v>
       </c>
       <c r="H6">
-        <v>290</v>
+        <v>379</v>
       </c>
       <c r="I6">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" si="2"/>
-        <v>62.098501070663815</v>
+        <v>81.330472103004297</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -5593,24 +5603,24 @@
         <v>88.888888888888886</v>
       </c>
       <c r="E8">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F8">
         <v>239</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="1"/>
-        <v>92.468619246861934</v>
+        <v>93.305439330543933</v>
       </c>
       <c r="H8">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I8">
         <v>530</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" si="2"/>
-        <v>89.056603773584911</v>
+        <v>89.433962264150949</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -5653,34 +5663,34 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C10">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>46.875</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="F10">
-        <v>253</v>
+        <v>444</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>77.927927927927925</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>929</v>
       </c>
       <c r="I10">
-        <v>650</v>
+        <v>1189</v>
       </c>
       <c r="J10" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>78.132884777123635</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -5689,39 +5699,39 @@
       </c>
       <c r="B12">
         <f>SUM(B2:B10)</f>
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="C12">
         <f t="shared" ref="C12:I12" si="3">SUM(C2:C10)</f>
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>56.451612903225815</v>
+        <v>67.307692307692307</v>
       </c>
       <c r="E12">
         <f t="shared" si="3"/>
-        <v>813</v>
+        <v>1215</v>
       </c>
       <c r="F12">
         <f t="shared" si="3"/>
-        <v>1287</v>
+        <v>1483</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="1"/>
-        <v>63.170163170163171</v>
+        <v>81.928523263654753</v>
       </c>
       <c r="H12">
         <f t="shared" si="3"/>
-        <v>1772</v>
+        <v>2795</v>
       </c>
       <c r="I12">
         <f t="shared" si="3"/>
-        <v>2849</v>
+        <v>3387</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" si="2"/>
-        <v>62.197262197262191</v>
+        <v>82.521405373486871</v>
       </c>
       <c r="K12" t="s">
         <v>23</v>
@@ -5730,7 +5740,7 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J13" s="1">
         <f>100-J12</f>
-        <v>37.802737802737809</v>
+        <v>17.478594626513129</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -5742,7 +5752,7 @@
       </c>
       <c r="M18">
         <f>I12-I4</f>
-        <v>2723</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="19" spans="12:13" x14ac:dyDescent="0.3">
@@ -5885,7 +5895,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
@@ -6045,7 +6055,7 @@
         <f>SUM(I2:I2)</f>
         <v>238</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <f>H4/I4*100</f>
         <v>0</v>
       </c>

--- a/doc/K2CoverageResults.xlsx
+++ b/doc/K2CoverageResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\openSUSE-Tumbleweed\home\ssilvestri\research\Kappa2\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D1BD6A-78B6-47B1-B898-5F419B1BAA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD9A299-9209-46D3-A7C2-6C7449CB23E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{834EB836-E108-4946-BBD2-E48878051BC8}"/>
   </bookViews>
@@ -18,7 +18,6 @@
     <sheet name="KCoder" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -349,19 +348,19 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>35</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>36</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>64</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -456,19 +455,19 @@
                   <c:v>91</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>230</c:v>
+                  <c:v>244</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>205</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>239</c:v>
+                  <c:v>243</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>444</c:v>
+                  <c:v>522</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -563,19 +562,19 @@
                   <c:v>247</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>466</c:v>
+                  <c:v>495</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>393</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>530</c:v>
+                  <c:v>549</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1189</c:v>
+                  <c:v>1367</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -901,28 +900,28 @@
                   <c:v>94.855305466237937</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60</c:v>
+                  <c:v>53.333333333333336</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>79.365079365079367</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>98.785425101214571</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>81.330472103004297</c:v>
+                  <c:v>86.868686868686879</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>94.402035623409674</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>89.433962264150949</c:v>
+                  <c:v>86.338797814207652</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>78.132884777123635</c:v>
+                  <c:v>86.027798098024874</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1218,10 +1217,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>82.521405373486871</c:v>
+                  <c:v>88.292277885413782</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17.478594626513129</c:v>
+                  <c:v>11.707722114586218</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5428,24 +5427,24 @@
         <v>33.333333333333329</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" ref="G3:G12" si="1">E3/F3*100</f>
-        <v>55.000000000000007</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I3">
         <v>45</v>
       </c>
       <c r="J3" s="1">
         <f t="shared" ref="J3:J12" si="2">H3/I3*100</f>
-        <v>60</v>
+        <v>53.333333333333336</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -5473,14 +5472,14 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>126</v>
       </c>
       <c r="J4" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>79.365079365079367</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -5523,34 +5522,34 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>65.714285714285708</v>
+        <v>65.853658536585371</v>
       </c>
       <c r="E6">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="F6">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="1"/>
-        <v>80.869565217391298</v>
+        <v>88.114754098360663</v>
       </c>
       <c r="H6">
-        <v>379</v>
+        <v>430</v>
       </c>
       <c r="I6">
-        <v>466</v>
+        <v>495</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" si="2"/>
-        <v>81.330472103004297</v>
+        <v>86.868686868686879</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -5596,31 +5595,31 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>88.888888888888886</v>
+        <v>86.486486486486484</v>
       </c>
       <c r="E8">
         <v>223</v>
       </c>
       <c r="F8">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="1"/>
-        <v>93.305439330543933</v>
+        <v>91.769547325102891</v>
       </c>
       <c r="H8">
         <v>474</v>
       </c>
       <c r="I8">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" si="2"/>
-        <v>89.433962264150949</v>
+        <v>86.338797814207652</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -5663,34 +5662,34 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C10">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>46.875</v>
+        <v>59.701492537313428</v>
       </c>
       <c r="E10">
-        <v>346</v>
+        <v>449</v>
       </c>
       <c r="F10">
-        <v>444</v>
+        <v>522</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="1"/>
-        <v>77.927927927927925</v>
+        <v>86.015325670498086</v>
       </c>
       <c r="H10">
-        <v>929</v>
+        <v>1176</v>
       </c>
       <c r="I10">
-        <v>1189</v>
+        <v>1367</v>
       </c>
       <c r="J10" s="1">
         <f t="shared" si="2"/>
-        <v>78.132884777123635</v>
+        <v>86.027798098024874</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -5699,39 +5698,39 @@
       </c>
       <c r="B12">
         <f>SUM(B2:B10)</f>
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C12">
         <f t="shared" ref="C12:I12" si="3">SUM(C2:C10)</f>
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>67.307692307692307</v>
+        <v>70.642201834862391</v>
       </c>
       <c r="E12">
         <f t="shared" si="3"/>
-        <v>1215</v>
+        <v>1346</v>
       </c>
       <c r="F12">
         <f t="shared" si="3"/>
-        <v>1483</v>
+        <v>1579</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="1"/>
-        <v>81.928523263654753</v>
+        <v>85.243825205826468</v>
       </c>
       <c r="H12">
         <f t="shared" si="3"/>
-        <v>2795</v>
+        <v>3190</v>
       </c>
       <c r="I12">
         <f t="shared" si="3"/>
-        <v>3387</v>
+        <v>3613</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" si="2"/>
-        <v>82.521405373486871</v>
+        <v>88.292277885413782</v>
       </c>
       <c r="K12" t="s">
         <v>23</v>
@@ -5740,7 +5739,7 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J13" s="1">
         <f>100-J12</f>
-        <v>17.478594626513129</v>
+        <v>11.707722114586218</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -5752,7 +5751,7 @@
       </c>
       <c r="M18">
         <f>I12-I4</f>
-        <v>3261</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="19" spans="12:13" x14ac:dyDescent="0.3">

--- a/doc/K2CoverageResults.xlsx
+++ b/doc/K2CoverageResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\openSUSE-Tumbleweed\home\ssilvestri\research\Kappa2\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD9A299-9209-46D3-A7C2-6C7449CB23E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44993DEE-DCA9-4B0A-8661-0CFF074E3D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{834EB836-E108-4946-BBD2-E48878051BC8}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{834EB836-E108-4946-BBD2-E48878051BC8}"/>
   </bookViews>
   <sheets>
     <sheet name="K2Stream" sheetId="1" r:id="rId1"/>
@@ -1445,13 +1445,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>30</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>32</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1499,13 +1499,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>134</c:v>
+                  <c:v>430</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21</c:v>
+                  <c:v>329</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>63</c:v>
+                  <c:v>325</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1555,13 +1555,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>845</c:v>
+                  <c:v>847</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>636</c:v>
+                  <c:v>621</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>423</c:v>
+                  <c:v>592</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1916,13 +1916,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.23612750885478156</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.322061191626409</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>89.86486486486487</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5805,34 +5805,34 @@
         <v>19</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1">
         <f>B2/C2*100</f>
-        <v>0</v>
+        <v>3.225806451612903</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>134</v>
+        <v>430</v>
       </c>
       <c r="G2" s="1">
         <f>E2/F2*100</f>
-        <v>0</v>
+        <v>0.46511627906976744</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="J2" s="1">
         <f>H2/I2*100</f>
-        <v>0</v>
+        <v>0.23612750885478156</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -5840,34 +5840,34 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1">
         <f t="shared" ref="D3:D4" si="0">B3/C3*100</f>
-        <v>0</v>
+        <v>4.3478260869565215</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" ref="G3:G4" si="1">E3/F3*100</f>
-        <v>0</v>
+        <v>0.60790273556231</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>636</v>
+        <v>621</v>
       </c>
       <c r="J3" s="1">
         <f t="shared" ref="J3:J4" si="2">H3/I3*100</f>
-        <v>0</v>
+        <v>0.322061191626409</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -5875,34 +5875,34 @@
         <v>21</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>77.777777777777786</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="F4">
-        <v>63</v>
+        <v>325</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>89.230769230769241</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>532</v>
       </c>
       <c r="I4">
-        <v>423</v>
+        <v>592</v>
       </c>
       <c r="J4" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>89.86486486486487</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -5911,39 +5911,39 @@
       </c>
       <c r="B6">
         <f>SUM(B2:B4)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <f>SUM(C2:C4)</f>
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" ref="D6" si="3">B6/C6*100</f>
-        <v>0</v>
+        <v>28.39506172839506</v>
       </c>
       <c r="E6">
         <f>SUM(E2:E4)</f>
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="F6">
         <f>SUM(F2:F4)</f>
-        <v>218</v>
+        <v>1084</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" ref="G6" si="4">E6/F6*100</f>
-        <v>0</v>
+        <v>27.121771217712176</v>
       </c>
       <c r="H6">
         <f>SUM(H2:H4)</f>
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="I6">
         <f>SUM(I2:I4)</f>
-        <v>1904</v>
+        <v>2060</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" ref="J6" si="5">H6/I6*100</f>
-        <v>0</v>
+        <v>26.019417475728158</v>
       </c>
     </row>
   </sheetData>

--- a/doc/K2CoverageResults.xlsx
+++ b/doc/K2CoverageResults.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\openSUSE-Tumbleweed\home\ssilvestri\research\Kappa2\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44993DEE-DCA9-4B0A-8661-0CFF074E3D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6A63A8-D3C2-4368-9919-F35FF5DE7894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{834EB836-E108-4946-BBD2-E48878051BC8}"/>
   </bookViews>
@@ -97,9 +97,6 @@
     <t>Phase 2</t>
   </si>
   <si>
-    <t>ast.rs</t>
-  </si>
-  <si>
     <t>coder.rs</t>
   </si>
   <si>
@@ -113,6 +110,9 @@
   </si>
   <si>
     <t>Uncovered</t>
+  </si>
+  <si>
+    <t>syntax_tree.rs</t>
   </si>
 </sst>
 </file>
@@ -1411,6 +1411,9 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>Functions</c:v>
+          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent2"/>
@@ -1427,13 +1430,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>ast.rs</c:v>
+                  <c:v>coder.rs</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>coder.rs</c:v>
+                  <c:v>parser.rs</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>parser.rs</c:v>
+                  <c:v>syntax_tree.rs</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1445,13 +1448,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>31</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>27</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1465,6 +1468,9 @@
         <c:ser>
           <c:idx val="4"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>Lines</c:v>
+          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent5"/>
@@ -1481,13 +1487,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>ast.rs</c:v>
+                  <c:v>coder.rs</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>coder.rs</c:v>
+                  <c:v>parser.rs</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>parser.rs</c:v>
+                  <c:v>syntax_tree.rs</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1499,13 +1505,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>430</c:v>
+                  <c:v>329</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>329</c:v>
+                  <c:v>325</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>325</c:v>
+                  <c:v>526</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1519,6 +1525,9 @@
         <c:ser>
           <c:idx val="7"/>
           <c:order val="2"/>
+          <c:tx>
+            <c:v>Regions</c:v>
+          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent2">
@@ -1537,13 +1546,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>ast.rs</c:v>
+                  <c:v>coder.rs</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>coder.rs</c:v>
+                  <c:v>parser.rs</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>parser.rs</c:v>
+                  <c:v>syntax_tree.rs</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1555,13 +1564,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>847</c:v>
+                  <c:v>621</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>621</c:v>
+                  <c:v>592</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>592</c:v>
+                  <c:v>1169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1898,13 +1907,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>ast.rs</c:v>
+                  <c:v>coder.rs</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>coder.rs</c:v>
+                  <c:v>parser.rs</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>parser.rs</c:v>
+                  <c:v>syntax_tree.rs</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1916,13 +1925,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.23612750885478156</c:v>
+                  <c:v>0.322061191626409</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.322061191626409</c:v>
+                  <c:v>89.86486486486487</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>89.86486486486487</c:v>
+                  <c:v>86.4841745081266</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2055,7 +2064,7 @@
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
+        <a:ln w="25400">
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
@@ -5733,7 +5742,7 @@
         <v>88.292277885413782</v>
       </c>
       <c r="K12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -5742,7 +5751,7 @@
         <v>11.707722114586218</v>
       </c>
       <c r="K13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="12:13" x14ac:dyDescent="0.3">
@@ -5773,6 +5782,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B342025-DC6A-446C-A7CB-D53CF62D5F59}">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
@@ -5808,31 +5820,31 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1">
-        <f>B2/C2*100</f>
-        <v>3.225806451612903</v>
+        <f t="shared" ref="D2:D3" si="0">B2/C2*100</f>
+        <v>4.3478260869565215</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>430</v>
+        <v>329</v>
       </c>
       <c r="G2" s="1">
-        <f>E2/F2*100</f>
-        <v>0.46511627906976744</v>
+        <f t="shared" ref="G2:G3" si="1">E2/F2*100</f>
+        <v>0.60790273556231</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
-        <v>847</v>
+        <v>621</v>
       </c>
       <c r="J2" s="1">
-        <f>H2/I2*100</f>
-        <v>0.23612750885478156</v>
+        <f t="shared" ref="J2:J3" si="2">H2/I2*100</f>
+        <v>0.322061191626409</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -5840,69 +5852,69 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1">
-        <f t="shared" ref="D3:D4" si="0">B3/C3*100</f>
-        <v>4.3478260869565215</v>
+        <f t="shared" si="0"/>
+        <v>77.777777777777786</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>290</v>
       </c>
       <c r="F3">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G4" si="1">E3/F3*100</f>
-        <v>0.60790273556231</v>
+        <f t="shared" si="1"/>
+        <v>89.230769230769241</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>532</v>
       </c>
       <c r="I3">
-        <v>621</v>
+        <v>592</v>
       </c>
       <c r="J3" s="1">
-        <f t="shared" ref="J3:J4" si="2">H3/I3*100</f>
-        <v>0.322061191626409</v>
+        <f t="shared" si="2"/>
+        <v>89.86486486486487</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1">
-        <f t="shared" si="0"/>
-        <v>77.777777777777786</v>
+        <f>B4/C4*100</f>
+        <v>81.081081081081081</v>
       </c>
       <c r="E4">
-        <v>290</v>
+        <v>437</v>
       </c>
       <c r="F4">
-        <v>325</v>
+        <v>526</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" si="1"/>
-        <v>89.230769230769241</v>
+        <f>E4/F4*100</f>
+        <v>83.079847908745251</v>
       </c>
       <c r="H4">
-        <v>532</v>
+        <v>1011</v>
       </c>
       <c r="I4">
-        <v>592</v>
+        <v>1169</v>
       </c>
       <c r="J4" s="1">
-        <f t="shared" si="2"/>
-        <v>89.86486486486487</v>
+        <f>H4/I4*100</f>
+        <v>86.4841745081266</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -5910,40 +5922,40 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <f>SUM(B2:B4)</f>
-        <v>23</v>
+        <f>SUM(B2:B3)</f>
+        <v>22</v>
       </c>
       <c r="C6">
-        <f>SUM(C2:C4)</f>
-        <v>81</v>
+        <f>SUM(C2:C3)</f>
+        <v>50</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" ref="D6" si="3">B6/C6*100</f>
-        <v>28.39506172839506</v>
+        <v>44</v>
       </c>
       <c r="E6">
-        <f>SUM(E2:E4)</f>
-        <v>294</v>
+        <f>SUM(E2:E3)</f>
+        <v>292</v>
       </c>
       <c r="F6">
-        <f>SUM(F2:F4)</f>
-        <v>1084</v>
+        <f>SUM(F2:F3)</f>
+        <v>654</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" ref="G6" si="4">E6/F6*100</f>
-        <v>27.121771217712176</v>
+        <v>44.648318042813457</v>
       </c>
       <c r="H6">
-        <f>SUM(H2:H4)</f>
-        <v>536</v>
+        <f>SUM(H2:H3)</f>
+        <v>534</v>
       </c>
       <c r="I6">
-        <f>SUM(I2:I4)</f>
-        <v>2060</v>
+        <f>SUM(I2:I3)</f>
+        <v>1213</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" ref="J6" si="5">H6/I6*100</f>
-        <v>26.019417475728158</v>
+        <v>44.023083264633136</v>
       </c>
     </row>
   </sheetData>
@@ -5985,7 +5997,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>0</v>
